--- a/input_data/Aircraft_Database.xlsx
+++ b/input_data/Aircraft_Database.xlsx
@@ -8,19 +8,32 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\johannc2\Box\05 Repositories\ACRP-Lab\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E29FAD39-775F-4DC5-A810-ACFF35809640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E989B230-BE5C-44D9-9142-7DA1E1B0A08A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="450" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="2" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>Aircraft</t>
   </si>
@@ -55,9 +68,6 @@
     <t>B777-300ER</t>
   </si>
   <si>
-    <t>A380</t>
-  </si>
-  <si>
     <t>70;45;90;45;70</t>
   </si>
   <si>
@@ -68,6 +78,27 @@
   </si>
   <si>
     <t>1.80;1.10;1.10;1.10;1.10;1.10;1.80</t>
+  </si>
+  <si>
+    <t>Tires in CLG</t>
+  </si>
+  <si>
+    <t>A380-800</t>
+  </si>
+  <si>
+    <t>2D</t>
+  </si>
+  <si>
+    <t>GW (lb)</t>
+  </si>
+  <si>
+    <t>GW (N)</t>
+  </si>
+  <si>
+    <t>Perc. GW on Gear</t>
+  </si>
+  <si>
+    <t>CLG</t>
   </si>
 </sst>
 </file>
@@ -441,51 +472,69 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ED32B4C5-4AEC-4AA8-B7EE-2BD0192A9A62}">
-  <dimension ref="A1:U37"/>
+  <dimension ref="A1:Z37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" style="3" customWidth="1"/>
-    <col min="2" max="2" width="14" style="3" customWidth="1"/>
-    <col min="3" max="3" width="14.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="22.7109375" style="3" customWidth="1"/>
-    <col min="5" max="5" width="21.140625" style="3" customWidth="1"/>
-    <col min="6" max="6" width="20.140625" style="3" customWidth="1"/>
-    <col min="7" max="7" width="31.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="32.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="24.42578125" style="3" customWidth="1"/>
-    <col min="10" max="16384" width="9.140625" style="3"/>
+    <col min="2" max="2" width="15.5703125" style="3" customWidth="1"/>
+    <col min="3" max="3" width="13" style="3" customWidth="1"/>
+    <col min="4" max="4" width="18" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9" style="3" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="14" style="3" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="22.7109375" style="3" customWidth="1"/>
+    <col min="10" max="10" width="21.140625" style="3" customWidth="1"/>
+    <col min="11" max="11" width="20.140625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="31.5703125" style="3" customWidth="1"/>
+    <col min="13" max="13" width="32.5703125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="22" style="3" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="9.140625" style="3"/>
+    <col min="17" max="17" width="13.140625" style="3" customWidth="1"/>
+    <col min="18" max="16384" width="9.140625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="J1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-      <c r="L1" s="2"/>
-      <c r="M1" s="2"/>
       <c r="N1" s="2"/>
       <c r="O1" s="2"/>
       <c r="P1" s="2"/>
@@ -494,37 +543,42 @@
       <c r="S1" s="2"/>
       <c r="T1" s="2"/>
       <c r="U1" s="2"/>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V1" s="2"/>
+      <c r="W1" s="2"/>
+      <c r="X1" s="2"/>
+      <c r="Y1" s="2"/>
+      <c r="Z1" s="2"/>
+    </row>
+    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="4">
+      <c r="B2" s="2"/>
+      <c r="C2" s="2"/>
+      <c r="D2" s="2"/>
+      <c r="E2" s="2"/>
+      <c r="F2" s="2"/>
+      <c r="G2" s="4">
         <v>153436.65</v>
       </c>
-      <c r="C2" s="6">
+      <c r="H2" s="6">
         <v>1.379</v>
       </c>
-      <c r="D2" s="5">
+      <c r="I2" s="5">
         <v>380</v>
       </c>
-      <c r="E2" s="5">
+      <c r="J2" s="5">
         <v>340</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>14</v>
+      </c>
       <c r="N2" s="2"/>
       <c r="O2" s="2"/>
       <c r="P2" s="2"/>
@@ -533,37 +587,54 @@
       <c r="S2" s="2"/>
       <c r="T2" s="2"/>
       <c r="U2" s="2"/>
-    </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+    </row>
+    <row r="3" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B3" s="4">
+        <v>1239000</v>
+      </c>
+      <c r="C3" s="4">
+        <f>B3*4.44822162</f>
+        <v>5511346.5871799998</v>
+      </c>
+      <c r="D3" s="2">
+        <v>0.38</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" s="2">
+        <v>8</v>
+      </c>
+      <c r="G3" s="4">
+        <f>C3*D3/F3</f>
+        <v>261788.96289105</v>
+      </c>
+      <c r="H3" s="6">
+        <v>1.45</v>
+      </c>
+      <c r="I3" s="5">
+        <v>560</v>
+      </c>
+      <c r="J3" s="5">
+        <v>360</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4">
-        <v>262100</v>
-      </c>
-      <c r="C3" s="6">
-        <v>1.45</v>
-      </c>
-      <c r="D3" s="5">
-        <v>560</v>
-      </c>
-      <c r="E3" s="5">
-        <v>360</v>
-      </c>
-      <c r="F3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="M3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="I3" s="2"/>
-      <c r="J3" s="2"/>
-      <c r="K3" s="2"/>
-      <c r="L3" s="2"/>
-      <c r="M3" s="2"/>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
       <c r="P3" s="2"/>
@@ -572,18 +643,23 @@
       <c r="S3" s="2"/>
       <c r="T3" s="2"/>
       <c r="U3" s="2"/>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V3" s="2"/>
+      <c r="W3" s="2"/>
+      <c r="X3" s="2"/>
+      <c r="Y3" s="2"/>
+      <c r="Z3" s="2"/>
+    </row>
+    <row r="4" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A4" s="2"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="5"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
+      <c r="B4" s="2"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="2"/>
       <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-      <c r="H4" s="2"/>
-      <c r="I4" s="2"/>
-      <c r="J4" s="2"/>
+      <c r="G4" s="4"/>
+      <c r="H4" s="5"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="5"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
@@ -595,18 +671,23 @@
       <c r="S4" s="2"/>
       <c r="T4" s="2"/>
       <c r="U4" s="2"/>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V4" s="2"/>
+      <c r="W4" s="2"/>
+      <c r="X4" s="2"/>
+      <c r="Y4" s="2"/>
+      <c r="Z4" s="2"/>
+    </row>
+    <row r="5" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A5" s="2"/>
-      <c r="B5" s="4"/>
-      <c r="C5" s="5"/>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
       <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-      <c r="H5" s="2"/>
-      <c r="I5" s="2"/>
-      <c r="J5" s="2"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="5"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="5"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -618,18 +699,23 @@
       <c r="S5" s="2"/>
       <c r="T5" s="2"/>
       <c r="U5" s="2"/>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V5" s="2"/>
+      <c r="W5" s="2"/>
+      <c r="X5" s="2"/>
+      <c r="Y5" s="2"/>
+      <c r="Z5" s="2"/>
+    </row>
+    <row r="6" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A6" s="2"/>
-      <c r="B6" s="4"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
       <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="5"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -641,18 +727,23 @@
       <c r="S6" s="2"/>
       <c r="T6" s="2"/>
       <c r="U6" s="2"/>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V6" s="2"/>
+      <c r="W6" s="2"/>
+      <c r="X6" s="2"/>
+      <c r="Y6" s="2"/>
+      <c r="Z6" s="2"/>
+    </row>
+    <row r="7" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A7" s="2"/>
-      <c r="B7" s="4"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
       <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-      <c r="H7" s="2"/>
-      <c r="I7" s="2"/>
-      <c r="J7" s="2"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="5"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -664,18 +755,23 @@
       <c r="S7" s="2"/>
       <c r="T7" s="2"/>
       <c r="U7" s="2"/>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V7" s="2"/>
+      <c r="W7" s="2"/>
+      <c r="X7" s="2"/>
+      <c r="Y7" s="2"/>
+      <c r="Z7" s="2"/>
+    </row>
+    <row r="8" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A8" s="2"/>
-      <c r="B8" s="4"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
+      <c r="B8" s="2"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="2"/>
       <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
+      <c r="G8" s="4"/>
+      <c r="H8" s="5"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="5"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -687,18 +783,23 @@
       <c r="S8" s="2"/>
       <c r="T8" s="2"/>
       <c r="U8" s="2"/>
-    </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V8" s="2"/>
+      <c r="W8" s="2"/>
+      <c r="X8" s="2"/>
+      <c r="Y8" s="2"/>
+      <c r="Z8" s="2"/>
+    </row>
+    <row r="9" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A9" s="2"/>
-      <c r="B9" s="4"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5"/>
-      <c r="E9" s="5"/>
+      <c r="B9" s="2"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="2"/>
       <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-      <c r="H9" s="2"/>
-      <c r="I9" s="2"/>
-      <c r="J9" s="2"/>
+      <c r="G9" s="4"/>
+      <c r="H9" s="5"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="5"/>
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -710,18 +811,23 @@
       <c r="S9" s="2"/>
       <c r="T9" s="2"/>
       <c r="U9" s="2"/>
-    </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V9" s="2"/>
+      <c r="W9" s="2"/>
+      <c r="X9" s="2"/>
+      <c r="Y9" s="2"/>
+      <c r="Z9" s="2"/>
+    </row>
+    <row r="10" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A10" s="2"/>
-      <c r="B10" s="4"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
+      <c r="B10" s="2"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="2"/>
       <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
+      <c r="G10" s="4"/>
+      <c r="H10" s="5"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="5"/>
       <c r="K10" s="2"/>
       <c r="L10" s="2"/>
       <c r="M10" s="2"/>
@@ -733,41 +839,51 @@
       <c r="S10" s="2"/>
       <c r="T10" s="2"/>
       <c r="U10" s="2"/>
-    </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V10" s="2"/>
+      <c r="W10" s="2"/>
+      <c r="X10" s="2"/>
+      <c r="Y10" s="2"/>
+      <c r="Z10" s="2"/>
+    </row>
+    <row r="11" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A11" s="2"/>
-      <c r="B11" s="4"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
+      <c r="B11" s="2"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="2"/>
       <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-      <c r="H11" s="2"/>
-      <c r="I11" s="2"/>
-      <c r="J11" s="2"/>
+      <c r="G11" s="4"/>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="5"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="2"/>
-      <c r="Q11" s="2"/>
+      <c r="N11" s="4"/>
+      <c r="O11" s="4"/>
+      <c r="P11" s="4"/>
+      <c r="Q11" s="4"/>
       <c r="R11" s="2"/>
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
       <c r="U11" s="2"/>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V11" s="2"/>
+      <c r="W11" s="2"/>
+      <c r="X11" s="2"/>
+      <c r="Y11" s="2"/>
+      <c r="Z11" s="2"/>
+    </row>
+    <row r="12" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A12" s="2"/>
-      <c r="B12" s="4"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
+      <c r="B12" s="2"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
       <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
+      <c r="G12" s="4"/>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5"/>
+      <c r="J12" s="5"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -779,18 +895,23 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
       <c r="U12" s="2"/>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V12" s="2"/>
+      <c r="W12" s="2"/>
+      <c r="X12" s="2"/>
+      <c r="Y12" s="2"/>
+      <c r="Z12" s="2"/>
+    </row>
+    <row r="13" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A13" s="2"/>
-      <c r="B13" s="4"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
       <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2"/>
-      <c r="I13" s="2"/>
-      <c r="J13" s="2"/>
+      <c r="G13" s="4"/>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5"/>
+      <c r="J13" s="5"/>
       <c r="K13" s="2"/>
       <c r="L13" s="2"/>
       <c r="M13" s="2"/>
@@ -802,18 +923,23 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
       <c r="U13" s="2"/>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V13" s="2"/>
+      <c r="W13" s="2"/>
+      <c r="X13" s="2"/>
+      <c r="Y13" s="2"/>
+      <c r="Z13" s="2"/>
+    </row>
+    <row r="14" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A14" s="2"/>
-      <c r="B14" s="4"/>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
+      <c r="B14" s="2"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="2"/>
+      <c r="E14" s="2"/>
       <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
+      <c r="G14" s="4"/>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5"/>
+      <c r="J14" s="5"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -825,18 +951,23 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
       <c r="U14" s="2"/>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V14" s="2"/>
+      <c r="W14" s="2"/>
+      <c r="X14" s="2"/>
+      <c r="Y14" s="2"/>
+      <c r="Z14" s="2"/>
+    </row>
+    <row r="15" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A15" s="2"/>
-      <c r="B15" s="4"/>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
+      <c r="B15" s="2"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="2"/>
+      <c r="E15" s="2"/>
       <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2"/>
-      <c r="I15" s="2"/>
-      <c r="J15" s="2"/>
+      <c r="G15" s="4"/>
+      <c r="H15" s="5"/>
+      <c r="I15" s="5"/>
+      <c r="J15" s="5"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -848,18 +979,23 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
       <c r="U15" s="2"/>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V15" s="2"/>
+      <c r="W15" s="2"/>
+      <c r="X15" s="2"/>
+      <c r="Y15" s="2"/>
+      <c r="Z15" s="2"/>
+    </row>
+    <row r="16" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A16" s="2"/>
-      <c r="B16" s="4"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
+      <c r="B16" s="2"/>
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
       <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2"/>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
+      <c r="G16" s="4"/>
+      <c r="H16" s="5"/>
+      <c r="I16" s="5"/>
+      <c r="J16" s="5"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -871,18 +1007,23 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
       <c r="U16" s="2"/>
-    </row>
-    <row r="17" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V16" s="2"/>
+      <c r="W16" s="2"/>
+      <c r="X16" s="2"/>
+      <c r="Y16" s="2"/>
+      <c r="Z16" s="2"/>
+    </row>
+    <row r="17" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A17" s="2"/>
-      <c r="B17" s="4"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
+      <c r="B17" s="2"/>
+      <c r="C17" s="2"/>
+      <c r="D17" s="2"/>
+      <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="2"/>
-      <c r="I17" s="2"/>
-      <c r="J17" s="2"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="5"/>
+      <c r="I17" s="5"/>
+      <c r="J17" s="5"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -894,18 +1035,23 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
       <c r="U17" s="2"/>
-    </row>
-    <row r="18" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V17" s="2"/>
+      <c r="W17" s="2"/>
+      <c r="X17" s="2"/>
+      <c r="Y17" s="2"/>
+      <c r="Z17" s="2"/>
+    </row>
+    <row r="18" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
-      <c r="B18" s="4"/>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
       <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2"/>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
+      <c r="G18" s="4"/>
+      <c r="H18" s="5"/>
+      <c r="I18" s="5"/>
+      <c r="J18" s="5"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -917,18 +1063,23 @@
       <c r="S18" s="2"/>
       <c r="T18" s="2"/>
       <c r="U18" s="2"/>
-    </row>
-    <row r="19" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V18" s="2"/>
+      <c r="W18" s="2"/>
+      <c r="X18" s="2"/>
+      <c r="Y18" s="2"/>
+      <c r="Z18" s="2"/>
+    </row>
+    <row r="19" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A19" s="2"/>
-      <c r="B19" s="4"/>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-      <c r="H19" s="2"/>
-      <c r="I19" s="2"/>
-      <c r="J19" s="2"/>
+      <c r="G19" s="4"/>
+      <c r="H19" s="5"/>
+      <c r="I19" s="5"/>
+      <c r="J19" s="5"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -940,18 +1091,23 @@
       <c r="S19" s="2"/>
       <c r="T19" s="2"/>
       <c r="U19" s="2"/>
-    </row>
-    <row r="20" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V19" s="2"/>
+      <c r="W19" s="2"/>
+      <c r="X19" s="2"/>
+      <c r="Y19" s="2"/>
+      <c r="Z19" s="2"/>
+    </row>
+    <row r="20" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A20" s="2"/>
-      <c r="B20" s="4"/>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
       <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-      <c r="H20" s="2"/>
-      <c r="I20" s="2"/>
-      <c r="J20" s="2"/>
+      <c r="G20" s="4"/>
+      <c r="H20" s="5"/>
+      <c r="I20" s="5"/>
+      <c r="J20" s="5"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -963,18 +1119,23 @@
       <c r="S20" s="2"/>
       <c r="T20" s="2"/>
       <c r="U20" s="2"/>
-    </row>
-    <row r="21" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V20" s="2"/>
+      <c r="W20" s="2"/>
+      <c r="X20" s="2"/>
+      <c r="Y20" s="2"/>
+      <c r="Z20" s="2"/>
+    </row>
+    <row r="21" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A21" s="2"/>
-      <c r="B21" s="4"/>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
       <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-      <c r="H21" s="2"/>
-      <c r="I21" s="2"/>
-      <c r="J21" s="2"/>
+      <c r="G21" s="4"/>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5"/>
+      <c r="J21" s="5"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -986,18 +1147,23 @@
       <c r="S21" s="2"/>
       <c r="T21" s="2"/>
       <c r="U21" s="2"/>
-    </row>
-    <row r="22" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V21" s="2"/>
+      <c r="W21" s="2"/>
+      <c r="X21" s="2"/>
+      <c r="Y21" s="2"/>
+      <c r="Z21" s="2"/>
+    </row>
+    <row r="22" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A22" s="2"/>
-      <c r="B22" s="4"/>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
       <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-      <c r="H22" s="2"/>
-      <c r="I22" s="2"/>
-      <c r="J22" s="2"/>
+      <c r="G22" s="4"/>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5"/>
+      <c r="J22" s="5"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1009,18 +1175,23 @@
       <c r="S22" s="2"/>
       <c r="T22" s="2"/>
       <c r="U22" s="2"/>
-    </row>
-    <row r="23" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V22" s="2"/>
+      <c r="W22" s="2"/>
+      <c r="X22" s="2"/>
+      <c r="Y22" s="2"/>
+      <c r="Z22" s="2"/>
+    </row>
+    <row r="23" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A23" s="2"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
       <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-      <c r="H23" s="2"/>
-      <c r="I23" s="2"/>
-      <c r="J23" s="2"/>
+      <c r="G23" s="4"/>
+      <c r="H23" s="5"/>
+      <c r="I23" s="5"/>
+      <c r="J23" s="5"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -1032,18 +1203,23 @@
       <c r="S23" s="2"/>
       <c r="T23" s="2"/>
       <c r="U23" s="2"/>
-    </row>
-    <row r="24" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V23" s="2"/>
+      <c r="W23" s="2"/>
+      <c r="X23" s="2"/>
+      <c r="Y23" s="2"/>
+      <c r="Z23" s="2"/>
+    </row>
+    <row r="24" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A24" s="2"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
       <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-      <c r="H24" s="2"/>
-      <c r="I24" s="2"/>
-      <c r="J24" s="2"/>
+      <c r="G24" s="4"/>
+      <c r="H24" s="5"/>
+      <c r="I24" s="5"/>
+      <c r="J24" s="5"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -1055,18 +1231,23 @@
       <c r="S24" s="2"/>
       <c r="T24" s="2"/>
       <c r="U24" s="2"/>
-    </row>
-    <row r="25" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V24" s="2"/>
+      <c r="W24" s="2"/>
+      <c r="X24" s="2"/>
+      <c r="Y24" s="2"/>
+      <c r="Z24" s="2"/>
+    </row>
+    <row r="25" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A25" s="2"/>
-      <c r="B25" s="4"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
       <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
-      <c r="H25" s="2"/>
-      <c r="I25" s="2"/>
-      <c r="J25" s="2"/>
+      <c r="G25" s="4"/>
+      <c r="H25" s="5"/>
+      <c r="I25" s="5"/>
+      <c r="J25" s="5"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -1078,18 +1259,23 @@
       <c r="S25" s="2"/>
       <c r="T25" s="2"/>
       <c r="U25" s="2"/>
-    </row>
-    <row r="26" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V25" s="2"/>
+      <c r="W25" s="2"/>
+      <c r="X25" s="2"/>
+      <c r="Y25" s="2"/>
+      <c r="Z25" s="2"/>
+    </row>
+    <row r="26" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A26" s="2"/>
-      <c r="B26" s="4"/>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
       <c r="F26" s="2"/>
-      <c r="G26" s="2"/>
-      <c r="H26" s="2"/>
-      <c r="I26" s="2"/>
-      <c r="J26" s="2"/>
+      <c r="G26" s="4"/>
+      <c r="H26" s="5"/>
+      <c r="I26" s="5"/>
+      <c r="J26" s="5"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1101,18 +1287,23 @@
       <c r="S26" s="2"/>
       <c r="T26" s="2"/>
       <c r="U26" s="2"/>
-    </row>
-    <row r="27" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+    </row>
+    <row r="27" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A27" s="2"/>
-      <c r="B27" s="4"/>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
       <c r="F27" s="2"/>
-      <c r="G27" s="2"/>
-      <c r="H27" s="2"/>
-      <c r="I27" s="2"/>
-      <c r="J27" s="2"/>
+      <c r="G27" s="4"/>
+      <c r="H27" s="5"/>
+      <c r="I27" s="5"/>
+      <c r="J27" s="5"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1124,106 +1315,161 @@
       <c r="S27" s="2"/>
       <c r="T27" s="2"/>
       <c r="U27" s="2"/>
-    </row>
-    <row r="28" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="V27" s="2"/>
+      <c r="W27" s="2"/>
+      <c r="X27" s="2"/>
+      <c r="Y27" s="2"/>
+      <c r="Z27" s="2"/>
+    </row>
+    <row r="28" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A28" s="2"/>
-      <c r="B28" s="4"/>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
       <c r="F28" s="2"/>
-      <c r="G28" s="2"/>
-      <c r="H28" s="2"/>
-    </row>
-    <row r="29" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="G28" s="4"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="5"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+    </row>
+    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A29" s="2"/>
-      <c r="B29" s="4"/>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
       <c r="F29" s="2"/>
-      <c r="G29" s="2"/>
-      <c r="H29" s="2"/>
-    </row>
-    <row r="30" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="G29" s="4"/>
+      <c r="H29" s="5"/>
+      <c r="I29" s="5"/>
+      <c r="J29" s="5"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+    </row>
+    <row r="30" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A30" s="2"/>
-      <c r="B30" s="4"/>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
       <c r="F30" s="2"/>
-      <c r="G30" s="2"/>
-      <c r="H30" s="2"/>
-    </row>
-    <row r="31" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="G30" s="4"/>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5"/>
+      <c r="J30" s="5"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+    </row>
+    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A31" s="2"/>
-      <c r="B31" s="4"/>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
+      <c r="B31" s="2"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
       <c r="F31" s="2"/>
-      <c r="G31" s="2"/>
-      <c r="H31" s="2"/>
-    </row>
-    <row r="32" spans="1:21" x14ac:dyDescent="0.25">
+      <c r="G31" s="4"/>
+      <c r="H31" s="5"/>
+      <c r="I31" s="5"/>
+      <c r="J31" s="5"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="2"/>
+      <c r="M31" s="2"/>
+    </row>
+    <row r="32" spans="1:26" x14ac:dyDescent="0.25">
       <c r="A32" s="2"/>
-      <c r="B32" s="4"/>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
+      <c r="B32" s="2"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
       <c r="F32" s="2"/>
-      <c r="G32" s="2"/>
-      <c r="H32" s="2"/>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G32" s="4"/>
+      <c r="H32" s="5"/>
+      <c r="I32" s="5"/>
+      <c r="J32" s="5"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="2"/>
+      <c r="M32" s="2"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="2"/>
-      <c r="B33" s="4"/>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
+      <c r="B33" s="2"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
       <c r="F33" s="2"/>
-      <c r="G33" s="2"/>
-      <c r="H33" s="2"/>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G33" s="4"/>
+      <c r="H33" s="5"/>
+      <c r="I33" s="5"/>
+      <c r="J33" s="5"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="2"/>
+      <c r="M33" s="2"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="2"/>
-      <c r="B34" s="4"/>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
+      <c r="B34" s="2"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
       <c r="F34" s="2"/>
-      <c r="G34" s="2"/>
-      <c r="H34" s="2"/>
-    </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G34" s="4"/>
+      <c r="H34" s="5"/>
+      <c r="I34" s="5"/>
+      <c r="J34" s="5"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="2"/>
+      <c r="M34" s="2"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
-      <c r="B35" s="4"/>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
+      <c r="B35" s="2"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
       <c r="F35" s="2"/>
-      <c r="G35" s="2"/>
-      <c r="H35" s="2"/>
-    </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G35" s="4"/>
+      <c r="H35" s="5"/>
+      <c r="I35" s="5"/>
+      <c r="J35" s="5"/>
+      <c r="K35" s="2"/>
+      <c r="L35" s="2"/>
+      <c r="M35" s="2"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
-      <c r="B36" s="4"/>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
+      <c r="B36" s="2"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
       <c r="F36" s="2"/>
-      <c r="G36" s="2"/>
-      <c r="H36" s="2"/>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="G36" s="4"/>
+      <c r="H36" s="5"/>
+      <c r="I36" s="5"/>
+      <c r="J36" s="5"/>
+      <c r="K36" s="2"/>
+      <c r="L36" s="2"/>
+      <c r="M36" s="2"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
-      <c r="B37" s="4"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
+      <c r="B37" s="2"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
       <c r="F37" s="2"/>
-      <c r="G37" s="2"/>
-      <c r="H37" s="2"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="2"/>
+      <c r="L37" s="2"/>
+      <c r="M37" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
